--- a/ARM Functions/Ability Edits/Type Low HP Boost (Blaze Overgrow Swarm Torrent).xlsx
+++ b/ARM Functions/Ability Edits/Type Low HP Boost (Blaze Overgrow Swarm Torrent).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C185BFAF-B004-453D-9613-4112B4F21973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78A2F50-FD60-4637-9678-2199CAA3FDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26511" yWindow="4611" windowWidth="24685" windowHeight="13149" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{664BA6B8-043A-4EF3-A83B-BDEF02BD0490}"/>
   </bookViews>
   <sheets>
     <sheet name="Original" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>notes</t>
   </si>
@@ -83,9 +83,6 @@
     <t>branch to boost function</t>
   </si>
   <si>
-    <t>mov r3, 0x400</t>
-  </si>
-  <si>
     <t>b 0x00077754</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
     <t>0B00A0E3</t>
   </si>
   <si>
-    <t>013BA0E3</t>
-  </si>
-  <si>
     <t>4D86FEEA</t>
   </si>
   <si>
@@ -125,10 +119,22 @@
     <t>0A00A0E3</t>
   </si>
   <si>
-    <t>000D4C0C</t>
-  </si>
-  <si>
-    <t>CE8AFEEA</t>
+    <t>mov r3, 0x200</t>
+  </si>
+  <si>
+    <t>023CA0E3</t>
+  </si>
+  <si>
+    <t>Set Bug</t>
+  </si>
+  <si>
+    <t>Set Water</t>
+  </si>
+  <si>
+    <t>000D4B9C</t>
+  </si>
+  <si>
+    <t>EA8AFEEA</t>
   </si>
 </sst>
 </file>
@@ -551,7 +557,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>11</v>
@@ -566,10 +572,10 @@
         <v>000D3DD4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -581,10 +587,10 @@
         <v>000D3DD8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -600,13 +606,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -615,10 +621,10 @@
         <v>000D5E14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>13</v>
@@ -630,10 +636,10 @@
         <v>000D5E18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -649,13 +655,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -664,10 +670,10 @@
         <v>000D87A4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -679,10 +685,10 @@
         <v>000D87A8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -695,28 +701,28 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="str">
         <f t="shared" ref="A19:A20" si="3">DEC2HEX(HEX2DEC(A18)+4,8)</f>
-        <v>000D4C10</v>
+        <v>000D4BA0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>13</v>
@@ -725,13 +731,13 @@
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="str">
         <f t="shared" si="3"/>
-        <v>000D4C14</v>
+        <v>000D4BA4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
